--- a/data/futures_foreign_cost.xlsx
+++ b/data/futures_foreign_cost.xlsx
@@ -214,12 +214,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$479</f>
+              <f>'對照總表'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$C$2:$C$479</f>
+              <f>'對照總表'!$C$2:$C$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -250,12 +250,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$479</f>
+              <f>'對照總表'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$F$2:$F$479</f>
+              <f>'對照總表'!$F$2:$F$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -286,12 +286,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$479</f>
+              <f>'對照總表'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$G$2:$G$479</f>
+              <f>'對照總表'!$G$2:$G$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -311,13 +311,13 @@
         <minorTickMark val="none"/>
         <crossAx val="100"/>
         <lblOffset val="100"/>
-        <tickLblSkip val="39"/>
+        <tickLblSkip val="40"/>
       </catAx>
       <valAx>
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="49000"/>
+          <max val="51000"/>
           <min val="17000"/>
         </scaling>
         <delete val="0"/>
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N479"/>
+  <dimension ref="A1:N487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -22223,6 +22223,374 @@
         <v>-16596608.69</v>
       </c>
     </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr"/>
+      <c r="C480" s="3" t="n">
+        <v>47767</v>
+      </c>
+      <c r="D480" s="4" t="n">
+        <v>-79029</v>
+      </c>
+      <c r="E480" s="4" t="n">
+        <v>-1998</v>
+      </c>
+      <c r="F480" s="5" t="n">
+        <v>45962.95</v>
+      </c>
+      <c r="G480" s="5" t="n">
+        <v>43928.95</v>
+      </c>
+      <c r="H480" s="6">
+        <f>IF(AND(ISNUMBER(F480),ISNUMBER(G480)),F480-G480,"")</f>
+        <v/>
+      </c>
+      <c r="I480" s="6">
+        <f>IF(AND(ISNUMBER(C480),ISNUMBER(F480)),C480-F480,"")</f>
+        <v/>
+      </c>
+      <c r="J480" s="6" t="n">
+        <v>-2851450.04</v>
+      </c>
+      <c r="K480" s="6" t="n">
+        <v>-173131.93</v>
+      </c>
+      <c r="L480" s="6" t="n">
+        <v>-3024581.97</v>
+      </c>
+      <c r="M480" s="6" t="n">
+        <v>-6066343.77</v>
+      </c>
+      <c r="N480" s="6" t="n">
+        <v>-16042831.9</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="B481" s="2" t="inlineStr"/>
+      <c r="C481" s="3" t="n">
+        <v>48330</v>
+      </c>
+      <c r="D481" s="4" t="n">
+        <v>-78151</v>
+      </c>
+      <c r="E481" s="4" t="n">
+        <v>878</v>
+      </c>
+      <c r="F481" s="5" t="n">
+        <v>45962.95</v>
+      </c>
+      <c r="G481" s="5" t="n">
+        <v>43928.95</v>
+      </c>
+      <c r="H481" s="6">
+        <f>IF(AND(ISNUMBER(F481),ISNUMBER(G481)),F481-G481,"")</f>
+        <v/>
+      </c>
+      <c r="I481" s="6">
+        <f>IF(AND(ISNUMBER(C481),ISNUMBER(F481)),C481-F481,"")</f>
+        <v/>
+      </c>
+      <c r="J481" s="6" t="n">
+        <v>-3699751.13</v>
+      </c>
+      <c r="K481" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="L481" s="6" t="n">
+        <v>-3914448.51</v>
+      </c>
+      <c r="M481" s="6" t="n">
+        <v>-6878927.89</v>
+      </c>
+      <c r="N481" s="6" t="n">
+        <v>-16933794.28</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/01</t>
+        </is>
+      </c>
+      <c r="B482" s="2" t="inlineStr"/>
+      <c r="C482" s="3" t="n">
+        <v>48685</v>
+      </c>
+      <c r="D482" s="4" t="n">
+        <v>-79554</v>
+      </c>
+      <c r="E482" s="4" t="n">
+        <v>-1403</v>
+      </c>
+      <c r="F482" s="5" t="n">
+        <v>46010.95</v>
+      </c>
+      <c r="G482" s="5" t="n">
+        <v>44003.52</v>
+      </c>
+      <c r="H482" s="6">
+        <f>IF(AND(ISNUMBER(F482),ISNUMBER(G482)),F482-G482,"")</f>
+        <v/>
+      </c>
+      <c r="I482" s="6">
+        <f>IF(AND(ISNUMBER(C482),ISNUMBER(F482)),C482-F482,"")</f>
+        <v/>
+      </c>
+      <c r="J482" s="6" t="n">
+        <v>-4254623.23</v>
+      </c>
+      <c r="K482" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="L482" s="6" t="n">
+        <v>-4469320.61</v>
+      </c>
+      <c r="M482" s="6" t="n">
+        <v>-7448602.09</v>
+      </c>
+      <c r="N482" s="6" t="n">
+        <v>-17503468.49</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/02</t>
+        </is>
+      </c>
+      <c r="B483" s="2" t="inlineStr"/>
+      <c r="C483" s="3" t="n">
+        <v>48671</v>
+      </c>
+      <c r="D483" s="4" t="n">
+        <v>-80304</v>
+      </c>
+      <c r="E483" s="4" t="n">
+        <v>-750</v>
+      </c>
+      <c r="F483" s="5" t="n">
+        <v>46035.8</v>
+      </c>
+      <c r="G483" s="5" t="n">
+        <v>44039.19</v>
+      </c>
+      <c r="H483" s="6">
+        <f>IF(AND(ISNUMBER(F483),ISNUMBER(G483)),F483-G483,"")</f>
+        <v/>
+      </c>
+      <c r="I483" s="6">
+        <f>IF(AND(ISNUMBER(C483),ISNUMBER(F483)),C483-F483,"")</f>
+        <v/>
+      </c>
+      <c r="J483" s="6" t="n">
+        <v>-4232348.11</v>
+      </c>
+      <c r="K483" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="L483" s="6" t="n">
+        <v>-4447045.49</v>
+      </c>
+      <c r="M483" s="6" t="n">
+        <v>-7439049.61</v>
+      </c>
+      <c r="N483" s="6" t="n">
+        <v>-17493916.01</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="B484" s="2" t="inlineStr"/>
+      <c r="C484" s="3" t="n">
+        <v>49949</v>
+      </c>
+      <c r="D484" s="4" t="n">
+        <v>-77004</v>
+      </c>
+      <c r="E484" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="F484" s="5" t="n">
+        <v>46035.8</v>
+      </c>
+      <c r="G484" s="5" t="n">
+        <v>44039.19</v>
+      </c>
+      <c r="H484" s="6">
+        <f>IF(AND(ISNUMBER(F484),ISNUMBER(G484)),F484-G484,"")</f>
+        <v/>
+      </c>
+      <c r="I484" s="6">
+        <f>IF(AND(ISNUMBER(C484),ISNUMBER(F484)),C484-F484,"")</f>
+        <v/>
+      </c>
+      <c r="J484" s="6" t="n">
+        <v>-6026646.9</v>
+      </c>
+      <c r="K484" s="6" t="n">
+        <v>-472968.83</v>
+      </c>
+      <c r="L484" s="6" t="n">
+        <v>-6499615.73</v>
+      </c>
+      <c r="M484" s="6" t="n">
+        <v>-9101572.710000001</v>
+      </c>
+      <c r="N484" s="6" t="n">
+        <v>-19503171.82</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="B485" s="2" t="inlineStr"/>
+      <c r="C485" s="3" t="n">
+        <v>50060</v>
+      </c>
+      <c r="D485" s="4" t="n">
+        <v>-79517</v>
+      </c>
+      <c r="E485" s="4" t="n">
+        <v>-2513</v>
+      </c>
+      <c r="F485" s="5" t="n">
+        <v>46162.97</v>
+      </c>
+      <c r="G485" s="5" t="n">
+        <v>44227.3</v>
+      </c>
+      <c r="H485" s="6">
+        <f>IF(AND(ISNUMBER(F485),ISNUMBER(G485)),F485-G485,"")</f>
+        <v/>
+      </c>
+      <c r="I485" s="6">
+        <f>IF(AND(ISNUMBER(C485),ISNUMBER(F485)),C485-F485,"")</f>
+        <v/>
+      </c>
+      <c r="J485" s="6" t="n">
+        <v>-6197595.78</v>
+      </c>
+      <c r="K485" s="6" t="n">
+        <v>-472968.83</v>
+      </c>
+      <c r="L485" s="6" t="n">
+        <v>-6670564.61</v>
+      </c>
+      <c r="M485" s="6" t="n">
+        <v>-9275972.380000001</v>
+      </c>
+      <c r="N485" s="6" t="n">
+        <v>-19677571.49</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr"/>
+      <c r="C486" s="3" t="n">
+        <v>49979</v>
+      </c>
+      <c r="D486" s="4" t="n">
+        <v>-79101</v>
+      </c>
+      <c r="E486" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="F486" s="5" t="n">
+        <v>46162.97</v>
+      </c>
+      <c r="G486" s="5" t="n">
+        <v>44227.3</v>
+      </c>
+      <c r="H486" s="6">
+        <f>IF(AND(ISNUMBER(F486),ISNUMBER(G486)),F486-G486,"")</f>
+        <v/>
+      </c>
+      <c r="I486" s="6">
+        <f>IF(AND(ISNUMBER(C486),ISNUMBER(F486)),C486-F486,"")</f>
+        <v/>
+      </c>
+      <c r="J486" s="6" t="n">
+        <v>-6037028.91</v>
+      </c>
+      <c r="K486" s="6" t="n">
+        <v>-504718.16</v>
+      </c>
+      <c r="L486" s="6" t="n">
+        <v>-6541747.07</v>
+      </c>
+      <c r="M486" s="6" t="n">
+        <v>-9099300.710000001</v>
+      </c>
+      <c r="N486" s="6" t="n">
+        <v>-19548489.72</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="B487" s="2" t="inlineStr"/>
+      <c r="C487" s="3" t="n">
+        <v>49349</v>
+      </c>
+      <c r="D487" s="4" t="n">
+        <v>-83194</v>
+      </c>
+      <c r="E487" s="4" t="n">
+        <v>-4093</v>
+      </c>
+      <c r="F487" s="5" t="n">
+        <v>46319.72</v>
+      </c>
+      <c r="G487" s="5" t="n">
+        <v>44491.19</v>
+      </c>
+      <c r="H487" s="6">
+        <f>IF(AND(ISNUMBER(F487),ISNUMBER(G487)),F487-G487,"")</f>
+        <v/>
+      </c>
+      <c r="I487" s="6">
+        <f>IF(AND(ISNUMBER(C487),ISNUMBER(F487)),C487-F487,"")</f>
+        <v/>
+      </c>
+      <c r="J487" s="6" t="n">
+        <v>-5040356.31</v>
+      </c>
+      <c r="K487" s="6" t="n">
+        <v>-504718.16</v>
+      </c>
+      <c r="L487" s="6" t="n">
+        <v>-5545074.47</v>
+      </c>
+      <c r="M487" s="6" t="n">
+        <v>-8082810.97</v>
+      </c>
+      <c r="N487" s="6" t="n">
+        <v>-18531999.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22234,7 +22602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V479"/>
+  <dimension ref="A1:V487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -55563,6 +55931,582 @@
       </c>
       <c r="V479" s="6" t="n">
         <v>-16596608.69</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/29</t>
+        </is>
+      </c>
+      <c r="B480" s="4" t="n">
+        <v>-1009</v>
+      </c>
+      <c r="C480" s="4" t="n">
+        <v>-9666227</v>
+      </c>
+      <c r="D480" s="4" t="n">
+        <v>-79029</v>
+      </c>
+      <c r="E480" s="4" t="n">
+        <v>-755298847</v>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G480" s="3" t="n">
+        <v>48194</v>
+      </c>
+      <c r="H480" s="3" t="n">
+        <v>47630</v>
+      </c>
+      <c r="I480" s="3" t="n">
+        <v>47767</v>
+      </c>
+      <c r="J480" s="3" t="n">
+        <v>47781</v>
+      </c>
+      <c r="K480" s="3" t="n">
+        <v>47930</v>
+      </c>
+      <c r="L480" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M480" s="4" t="n">
+        <v>-1998</v>
+      </c>
+      <c r="N480" s="5" t="n">
+        <v>45962.95</v>
+      </c>
+      <c r="O480" s="6" t="n">
+        <v>-2851450.04</v>
+      </c>
+      <c r="P480" s="6" t="n">
+        <v>-173131.93</v>
+      </c>
+      <c r="Q480" s="6" t="n">
+        <v>-3024581.97</v>
+      </c>
+      <c r="R480" s="5" t="n">
+        <v>47900.03</v>
+      </c>
+      <c r="S480" s="5" t="n">
+        <v>43928.95</v>
+      </c>
+      <c r="T480" s="6" t="n">
+        <v>-6066343.77</v>
+      </c>
+      <c r="U480" s="6" t="n">
+        <v>-9976488.130000001</v>
+      </c>
+      <c r="V480" s="6" t="n">
+        <v>-16042831.9</v>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" s="2" t="inlineStr">
+        <is>
+          <t>2026/09/30</t>
+        </is>
+      </c>
+      <c r="B481" s="4" t="n">
+        <v>846</v>
+      </c>
+      <c r="C481" s="4" t="n">
+        <v>8187995</v>
+      </c>
+      <c r="D481" s="4" t="n">
+        <v>-78151</v>
+      </c>
+      <c r="E481" s="4" t="n">
+        <v>-755498847</v>
+      </c>
+      <c r="F481" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G481" s="3" t="n">
+        <v>48646</v>
+      </c>
+      <c r="H481" s="3" t="n">
+        <v>48230</v>
+      </c>
+      <c r="I481" s="3" t="n">
+        <v>48330</v>
+      </c>
+      <c r="J481" s="3" t="n">
+        <v>48330</v>
+      </c>
+      <c r="K481" s="3" t="n">
+        <v>48494</v>
+      </c>
+      <c r="L481" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M481" s="4" t="n">
+        <v>878</v>
+      </c>
+      <c r="N481" s="5" t="n">
+        <v>45962.95</v>
+      </c>
+      <c r="O481" s="6" t="n">
+        <v>-3699751.13</v>
+      </c>
+      <c r="P481" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="Q481" s="6" t="n">
+        <v>-3914448.51</v>
+      </c>
+      <c r="R481" s="5" t="n">
+        <v>48392.41</v>
+      </c>
+      <c r="S481" s="5" t="n">
+        <v>43928.95</v>
+      </c>
+      <c r="T481" s="6" t="n">
+        <v>-6878927.89</v>
+      </c>
+      <c r="U481" s="6" t="n">
+        <v>-10054866.4</v>
+      </c>
+      <c r="V481" s="6" t="n">
+        <v>-16933794.28</v>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/01</t>
+        </is>
+      </c>
+      <c r="B482" s="4" t="n">
+        <v>-1389</v>
+      </c>
+      <c r="C482" s="4" t="n">
+        <v>-13378149</v>
+      </c>
+      <c r="D482" s="4" t="n">
+        <v>-79554</v>
+      </c>
+      <c r="E482" s="4" t="n">
+        <v>-774905393</v>
+      </c>
+      <c r="F482" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G482" s="3" t="n">
+        <v>48719</v>
+      </c>
+      <c r="H482" s="3" t="n">
+        <v>48168</v>
+      </c>
+      <c r="I482" s="3" t="n">
+        <v>48685</v>
+      </c>
+      <c r="J482" s="3" t="n">
+        <v>48698</v>
+      </c>
+      <c r="K482" s="3" t="n">
+        <v>48858</v>
+      </c>
+      <c r="L482" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M482" s="4" t="n">
+        <v>-1403</v>
+      </c>
+      <c r="N482" s="5" t="n">
+        <v>46010.95</v>
+      </c>
+      <c r="O482" s="6" t="n">
+        <v>-4254623.23</v>
+      </c>
+      <c r="P482" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="Q482" s="6" t="n">
+        <v>-4469320.61</v>
+      </c>
+      <c r="R482" s="5" t="n">
+        <v>48157.48</v>
+      </c>
+      <c r="S482" s="5" t="n">
+        <v>44003.52</v>
+      </c>
+      <c r="T482" s="6" t="n">
+        <v>-7448602.09</v>
+      </c>
+      <c r="U482" s="6" t="n">
+        <v>-10054866.4</v>
+      </c>
+      <c r="V482" s="6" t="n">
+        <v>-17503468.49</v>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/02</t>
+        </is>
+      </c>
+      <c r="B483" s="4" t="n">
+        <v>-802</v>
+      </c>
+      <c r="C483" s="4" t="n">
+        <v>-7670781</v>
+      </c>
+      <c r="D483" s="4" t="n">
+        <v>-80304</v>
+      </c>
+      <c r="E483" s="4" t="n">
+        <v>-781742101</v>
+      </c>
+      <c r="F483" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G483" s="3" t="n">
+        <v>48802</v>
+      </c>
+      <c r="H483" s="3" t="n">
+        <v>48472</v>
+      </c>
+      <c r="I483" s="3" t="n">
+        <v>48671</v>
+      </c>
+      <c r="J483" s="3" t="n">
+        <v>48669</v>
+      </c>
+      <c r="K483" s="3" t="n">
+        <v>48841</v>
+      </c>
+      <c r="L483" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M483" s="4" t="n">
+        <v>-750</v>
+      </c>
+      <c r="N483" s="5" t="n">
+        <v>46035.8</v>
+      </c>
+      <c r="O483" s="6" t="n">
+        <v>-4232348.11</v>
+      </c>
+      <c r="P483" s="6" t="n">
+        <v>-214697.38</v>
+      </c>
+      <c r="Q483" s="6" t="n">
+        <v>-4447045.49</v>
+      </c>
+      <c r="R483" s="5" t="n">
+        <v>47822.82</v>
+      </c>
+      <c r="S483" s="5" t="n">
+        <v>44039.19</v>
+      </c>
+      <c r="T483" s="6" t="n">
+        <v>-7439049.61</v>
+      </c>
+      <c r="U483" s="6" t="n">
+        <v>-10054866.4</v>
+      </c>
+      <c r="V483" s="6" t="n">
+        <v>-17493916.01</v>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="B484" s="4" t="n">
+        <v>3295</v>
+      </c>
+      <c r="C484" s="4" t="n">
+        <v>32483903</v>
+      </c>
+      <c r="D484" s="4" t="n">
+        <v>-77004</v>
+      </c>
+      <c r="E484" s="4" t="n">
+        <v>-769250525</v>
+      </c>
+      <c r="F484" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G484" s="3" t="n">
+        <v>50097</v>
+      </c>
+      <c r="H484" s="3" t="n">
+        <v>49461</v>
+      </c>
+      <c r="I484" s="3" t="n">
+        <v>49949</v>
+      </c>
+      <c r="J484" s="3" t="n">
+        <v>49944</v>
+      </c>
+      <c r="K484" s="3" t="n">
+        <v>50125</v>
+      </c>
+      <c r="L484" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M484" s="4" t="n">
+        <v>3300</v>
+      </c>
+      <c r="N484" s="5" t="n">
+        <v>46035.8</v>
+      </c>
+      <c r="O484" s="6" t="n">
+        <v>-6026646.9</v>
+      </c>
+      <c r="P484" s="6" t="n">
+        <v>-472968.83</v>
+      </c>
+      <c r="Q484" s="6" t="n">
+        <v>-6499615.73</v>
+      </c>
+      <c r="R484" s="5" t="n">
+        <v>49292.72</v>
+      </c>
+      <c r="S484" s="5" t="n">
+        <v>44039.19</v>
+      </c>
+      <c r="T484" s="6" t="n">
+        <v>-9101572.710000001</v>
+      </c>
+      <c r="U484" s="6" t="n">
+        <v>-10401599.11</v>
+      </c>
+      <c r="V484" s="6" t="n">
+        <v>-19503171.82</v>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/06</t>
+        </is>
+      </c>
+      <c r="B485" s="4" t="n">
+        <v>-2479</v>
+      </c>
+      <c r="C485" s="4" t="n">
+        <v>-24785707</v>
+      </c>
+      <c r="D485" s="4" t="n">
+        <v>-79517</v>
+      </c>
+      <c r="E485" s="4" t="n">
+        <v>-796566215</v>
+      </c>
+      <c r="F485" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G485" s="3" t="n">
+        <v>50194</v>
+      </c>
+      <c r="H485" s="3" t="n">
+        <v>49720</v>
+      </c>
+      <c r="I485" s="3" t="n">
+        <v>50060</v>
+      </c>
+      <c r="J485" s="3" t="n">
+        <v>50082</v>
+      </c>
+      <c r="K485" s="3" t="n">
+        <v>50244</v>
+      </c>
+      <c r="L485" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M485" s="4" t="n">
+        <v>-2513</v>
+      </c>
+      <c r="N485" s="5" t="n">
+        <v>46162.97</v>
+      </c>
+      <c r="O485" s="6" t="n">
+        <v>-6197595.78</v>
+      </c>
+      <c r="P485" s="6" t="n">
+        <v>-472968.83</v>
+      </c>
+      <c r="Q485" s="6" t="n">
+        <v>-6670564.61</v>
+      </c>
+      <c r="R485" s="5" t="n">
+        <v>49991.34</v>
+      </c>
+      <c r="S485" s="5" t="n">
+        <v>44227.3</v>
+      </c>
+      <c r="T485" s="6" t="n">
+        <v>-9275972.380000001</v>
+      </c>
+      <c r="U485" s="6" t="n">
+        <v>-10401599.11</v>
+      </c>
+      <c r="V485" s="6" t="n">
+        <v>-19677571.49</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/07</t>
+        </is>
+      </c>
+      <c r="B486" s="4" t="n">
+        <v>408</v>
+      </c>
+      <c r="C486" s="4" t="n">
+        <v>4075695</v>
+      </c>
+      <c r="D486" s="4" t="n">
+        <v>-79101</v>
+      </c>
+      <c r="E486" s="4" t="n">
+        <v>-790597660</v>
+      </c>
+      <c r="F486" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G486" s="3" t="n">
+        <v>50117</v>
+      </c>
+      <c r="H486" s="3" t="n">
+        <v>49842</v>
+      </c>
+      <c r="I486" s="3" t="n">
+        <v>49979</v>
+      </c>
+      <c r="J486" s="3" t="n">
+        <v>49968</v>
+      </c>
+      <c r="K486" s="3" t="n">
+        <v>50143</v>
+      </c>
+      <c r="L486" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M486" s="4" t="n">
+        <v>416</v>
+      </c>
+      <c r="N486" s="5" t="n">
+        <v>46162.97</v>
+      </c>
+      <c r="O486" s="6" t="n">
+        <v>-6037028.91</v>
+      </c>
+      <c r="P486" s="6" t="n">
+        <v>-504718.16</v>
+      </c>
+      <c r="Q486" s="6" t="n">
+        <v>-6541747.07</v>
+      </c>
+      <c r="R486" s="5" t="n">
+        <v>49947.24</v>
+      </c>
+      <c r="S486" s="5" t="n">
+        <v>44227.3</v>
+      </c>
+      <c r="T486" s="6" t="n">
+        <v>-9099300.710000001</v>
+      </c>
+      <c r="U486" s="6" t="n">
+        <v>-10449189.01</v>
+      </c>
+      <c r="V486" s="6" t="n">
+        <v>-19548489.72</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" s="2" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+      <c r="B487" s="4" t="n">
+        <v>-4048</v>
+      </c>
+      <c r="C487" s="4" t="n">
+        <v>-40148943</v>
+      </c>
+      <c r="D487" s="4" t="n">
+        <v>-83194</v>
+      </c>
+      <c r="E487" s="4" t="n">
+        <v>-821357330</v>
+      </c>
+      <c r="F487" s="2" t="inlineStr">
+        <is>
+          <t>202610</t>
+        </is>
+      </c>
+      <c r="G487" s="3" t="n">
+        <v>49692</v>
+      </c>
+      <c r="H487" s="3" t="n">
+        <v>49333</v>
+      </c>
+      <c r="I487" s="3" t="n">
+        <v>49349</v>
+      </c>
+      <c r="J487" s="3" t="n">
+        <v>49357</v>
+      </c>
+      <c r="K487" s="3" t="n">
+        <v>49546</v>
+      </c>
+      <c r="L487" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M487" s="4" t="n">
+        <v>-4093</v>
+      </c>
+      <c r="N487" s="5" t="n">
+        <v>46319.72</v>
+      </c>
+      <c r="O487" s="6" t="n">
+        <v>-5040356.31</v>
+      </c>
+      <c r="P487" s="6" t="n">
+        <v>-504718.16</v>
+      </c>
+      <c r="Q487" s="6" t="n">
+        <v>-5545074.47</v>
+      </c>
+      <c r="R487" s="5" t="n">
+        <v>49591.09</v>
+      </c>
+      <c r="S487" s="5" t="n">
+        <v>44491.19</v>
+      </c>
+      <c r="T487" s="6" t="n">
+        <v>-8082810.97</v>
+      </c>
+      <c r="U487" s="6" t="n">
+        <v>-10449189.01</v>
+      </c>
+      <c r="V487" s="6" t="n">
+        <v>-18531999.99</v>
       </c>
     </row>
   </sheetData>
@@ -55713,7 +56657,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026/09/24</t>
+          <t>2026/10/08</t>
         </is>
       </c>
     </row>

--- a/data/futures_foreign_cost.xlsx
+++ b/data/futures_foreign_cost.xlsx
@@ -7,10 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="對照總表" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="期交所原始" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="走勢圖" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="說明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="外資對照" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="投信對照" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="自營商對照" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="走勢圖" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="外資原始" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="投信原始" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="自營商原始" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="說明" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -193,13 +197,13 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'對照總表'!C1</f>
+              <f>'外資對照'!C1</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln w="15000">
               <a:solidFill>
-                <a:srgbClr val="6B7280"/>
+                <a:srgbClr val="2A78D6"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -214,12 +218,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$487</f>
+              <f>'外資對照'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$C$2:$C$487</f>
+              <f>'外資對照'!$C$2:$C$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -229,13 +233,13 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'對照總表'!F1</f>
+              <f>'外資對照'!F1</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln w="15000">
               <a:solidFill>
-                <a:srgbClr val="DC2626"/>
+                <a:srgbClr val="B07400"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -250,12 +254,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$487</f>
+              <f>'外資對照'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$F$2:$F$487</f>
+              <f>'外資對照'!$F$2:$F$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -265,13 +269,13 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'對照總表'!G1</f>
+              <f>'外資對照'!G1</f>
             </strRef>
           </tx>
           <spPr>
             <a:ln w="15000">
               <a:solidFill>
-                <a:srgbClr val="2563EB"/>
+                <a:srgbClr val="11906A"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
             </a:ln>
@@ -286,12 +290,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'對照總表'!$A$2:$A$487</f>
+              <f>'外資對照'!$A$2:$A$487</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'對照總表'!$G$2:$G$487</f>
+              <f>'外資對照'!$G$2:$G$487</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -361,7 +365,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10080000" cy="3960000"/>
+    <ext cx="10080000" cy="3600000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -22602,6 +22606,224 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19.6" customWidth="1" min="8" max="8"/>
+    <col width="14.8" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>結算日</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>近月收盤</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉淨口數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>淨口數變動</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>重置法成本</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>連續法成本</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>成本差異(重置-連續)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>收盤距重置法成本</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>重置法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>重置法已實現(萬元)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>重置法總損益(萬元)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>連續法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>連續法總損益(萬元)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="19.6" customWidth="1" min="8" max="8"/>
+    <col width="14.8" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>結算日</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>近月收盤</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉淨口數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>淨口數變動</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>重置法成本</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>連續法成本</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>成本差異(重置-連續)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>收盤距重置法成本</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>重置法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>重置法已實現(萬元)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>重置法總損益(萬元)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>連續法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>連續法總損益(萬元)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:V487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -56514,27 +56736,313 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:V1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14.8" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="11.6" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>多空交易口數淨額</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>多空交易契約金額淨額(千元)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉淨口數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉契約金額淨額(千元)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>近月契約</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>近月最高</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>近月最低</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>近月收盤</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>近月結算價</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>次月收盤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>結算日</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>淨口數變動</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>重置法成本</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>重置法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>重置法已實現(萬元)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>重置法總損益(萬元)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>當日成交均價</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>連續法成本</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>連續法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>連續法已實現累計(萬元)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>連續法總損益(萬元)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14.8" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="11.6" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="18" customWidth="1" min="16" max="16"/>
+    <col width="18" customWidth="1" min="17" max="17"/>
+    <col width="11.6" customWidth="1" min="18" max="18"/>
+    <col width="11" customWidth="1" min="19" max="19"/>
+    <col width="18" customWidth="1" min="20" max="20"/>
+    <col width="20" customWidth="1" min="21" max="21"/>
+    <col width="18" customWidth="1" min="22" max="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>日期</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>多空交易口數淨額</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>多空交易契約金額淨額(千元)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉淨口數</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>未平倉契約金額淨額(千元)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>近月契約</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>近月最高</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>近月最低</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>近月收盤</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>近月結算價</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>次月收盤</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>結算日</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>淨口數變動</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>重置法成本</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>重置法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>重置法已實現(萬元)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>重置法總損益(萬元)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>當日成交均價</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>連續法成本</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>連續法未實現(萬元)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>連續法已實現累計(萬元)</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>連續法總損益(萬元)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -56561,7 +57069,7 @@
       </c>
       <c r="B2" s="9" t="inlineStr">
         <is>
-          <t>台指期外資持倉成本：以期交所官方資料自算兩種成本線並列對照，GitHub Actions 每交易日更新</t>
+          <t>台指期三大法人（外資、投信、自營商）持倉成本：以期交所官方資料自算兩種成本線並列對照，GitHub Actions 每交易日更新</t>
         </is>
       </c>
     </row>
@@ -56573,7 +57081,7 @@
       </c>
       <c r="B3" s="9" t="inlineStr">
         <is>
-          <t>臺灣期貨交易所：三大法人-區分各期貨契約(TXF 外資及陸資)、期貨每日交易行情(TX 月契約一般盤)</t>
+          <t>臺灣期貨交易所：三大法人-區分各期貨契約(TXF)、期貨每日交易行情(TX 月契約一般盤)</t>
         </is>
       </c>
     </row>
@@ -56609,65 +57117,77 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>近月結算價為 0（到期日）或隔日近月換月者標為結算日，對照總表以黃底標示</t>
+          <t>近月結算價為 0（到期日）或隔日近月換月者標為結算日，對照表以黃底標示</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>損益單位</t>
+          <t>自營商</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>萬元（每點 200 元）</t>
+          <t>自營商部位常在多空間翻轉、口數小，持倉成本參考性較低，請搭配淨口數一起看</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>色彩慣例</t>
+          <t>損益單位</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>台股慣例：正值/增加=紅，負值/減少=綠</t>
+          <t>萬元（每點 200 元）</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>公式欄</t>
+          <t>色彩慣例</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>對照總表 H、I 欄為公式，兩邊皆有數值時才計算</t>
+          <t>台股慣例：正值/增加=紅，負值/減少=綠</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>資料日期</t>
+          <t>公式欄</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>2026/10/08</t>
+          <t>各對照表 H、I 欄為公式，兩邊皆有數值時才計算</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
+          <t>資料日期</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>2026/10/08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="inlineStr">
+        <is>
           <t>免責聲明</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>數據僅供參考，不構成任何投資建議；資料以期交所公告為準，使用者須遵守期交所資料使用規範</t>
         </is>
